--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486340_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486340_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8773</v>
+        <v>3.341</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8714</v>
+        <v>0.8721</v>
       </c>
       <c r="F2" t="n">
-        <v>3.006</v>
+        <v>2.4689</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6701</v>
+        <v>3.6867</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2771</v>
+        <v>0.5868</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3929</v>
+        <v>3.0998</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0478</v>
+        <v>2.7983</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4015</v>
+        <v>0.0611</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6463</v>
+        <v>2.7372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6222</v>
+        <v>0.8883</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8757</v>
+        <v>0.5258</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2534</v>
+        <v>0.3626</v>
       </c>
       <c r="P2" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9675</v>
+        <v>-0.0634</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1286</v>
+        <v>-0.0769</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8389</v>
+        <v>0.0135</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1952</v>
+        <v>-0.9347</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1257</v>
+        <v>2.9564</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2079</v>
+        <v>0.5361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9177999999999999</v>
+        <v>2.4203</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5138</v>
+        <v>2.6701</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2047</v>
+        <v>1.2771</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6909</v>
+        <v>1.3929</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0415</v>
+        <v>2.0478</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8614</v>
+        <v>0.4015</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8199</v>
+        <v>1.6463</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4723</v>
+        <v>0.6222</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3433</v>
+        <v>0.8757</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1291</v>
+        <v>-0.2534</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4591</v>
+        <v>0.0466</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4062</v>
+        <v>-0.2067</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0529</v>
+        <v>0.2532</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3698</v>
+        <v>-0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.002</v>
+        <v>2.794</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8721</v>
+        <v>1.2684</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1299</v>
+        <v>1.5256</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6867</v>
+        <v>3.7812</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5868</v>
+        <v>2.4329</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0998</v>
+        <v>1.3483</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7983</v>
+        <v>2.708</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0611</v>
+        <v>1.8067</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7372</v>
+        <v>0.9013</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8883</v>
+        <v>1.0732</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5258</v>
+        <v>0.6262</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3626</v>
+        <v>0.447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4024</v>
+        <v>0.0574</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0769</v>
+        <v>-0.2199</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3255</v>
+        <v>0.2773</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9347</v>
+        <v>-0.1745</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.5443</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2159</v>
+        <v>2.5669</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5979</v>
+        <v>1.6491</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6181</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7812</v>
+        <v>1.5138</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4329</v>
+        <v>2.2047</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3483</v>
+        <v>-0.6909</v>
       </c>
       <c r="J5" t="n">
-        <v>2.708</v>
+        <v>1.0415</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8067</v>
+        <v>1.8614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9013</v>
+        <v>-0.8199</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0732</v>
+        <v>0.4723</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6262</v>
+        <v>0.3433</v>
       </c>
       <c r="O5" t="n">
-        <v>0.447</v>
+        <v>0.1291</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.0997</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8904</v>
+        <v>-0.1526</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3698</v>
+        <v>0.0529</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1745</v>
+        <v>-0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
         <v>-1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7554</v>
+        <v>1.6359</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9732</v>
+        <v>2.638</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2178</v>
+        <v>-1.0021</v>
       </c>
       <c r="G6" t="n">
         <v>3.1659</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0669</v>
+        <v>-0.0526</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4747</v>
+        <v>0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4077</v>
+        <v>-0.192</v>
       </c>
       <c r="V6" t="n">
         <v>-1.695</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5461</v>
+        <v>0.5595</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9619</v>
+        <v>3.0678</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4158</v>
+        <v>-2.5083</v>
       </c>
       <c r="G7" t="n">
         <v>1.5782</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>0.3734</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2882</v>
+        <v>0.3942</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0717</v>
+        <v>-0.0207</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7395</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1046</v>
+        <v>0.231</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0254</v>
+        <v>1.1019</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1299</v>
+        <v>-0.871</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7328</v>
+        <v>1.9615</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1612</v>
+        <v>-0.198</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8941</v>
+        <v>2.1595</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1229</v>
+        <v>2.8327</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8879</v>
+        <v>0.4197</v>
       </c>
       <c r="L8" t="n">
-        <v>0.765</v>
+        <v>2.4129</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8557</v>
+        <v>-0.8712</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7267</v>
+        <v>-0.6178</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1291</v>
+        <v>-0.2534</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5858</v>
+        <v>-0.861</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2511</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.6099</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>-1.3045</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X8" t="n">
         <v>-1.13</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.636</v>
+        <v>0.0622</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5432</v>
+        <v>-0.9136</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1792</v>
+        <v>0.9758</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9615</v>
+        <v>0.7328</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.198</v>
+        <v>-0.1612</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1595</v>
+        <v>0.8941</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8327</v>
+        <v>-0.1229</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4197</v>
+        <v>-0.8879</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4129</v>
+        <v>0.765</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8712</v>
+        <v>0.8557</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6178</v>
+        <v>0.7267</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2534</v>
+        <v>0.1291</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.728</v>
+        <v>-0.6282</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8099</v>
+        <v>-0.5732</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9181</v>
+        <v>-0.055</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3045</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9591</v>
+        <v>-0.9398</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0128</v>
+        <v>-0.901</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0537</v>
+        <v>-0.0388</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0257</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1318</v>
+        <v>0.1511</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1318</v>
+        <v>0.0394</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.372</v>
+        <v>-1.2602</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2245</v>
+        <v>-1.1128</v>
       </c>
       <c r="F11" t="n">
         <v>-0.1475</v>
@@ -1312,10 +1312,10 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4884</v>
+        <v>-2.7755</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7225</v>
+        <v>-4.1637</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2341</v>
+        <v>1.3882</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0496</v>
@@ -1390,13 +1390,13 @@
         <v>2.3926</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7863</v>
+        <v>-1.0734</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1524</v>
+        <v>-0.5936</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6339</v>
+        <v>-0.4798</v>
       </c>
       <c r="V12" t="n">
         <v>2.2599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1715</v>
+        <v>9.171400000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>4.042400000000001</v>
+        <v>4.042299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1292</v>
+        <v>5.128900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>13.6499</v>
@@ -1453,7 +1453,7 @@
         <v>1.0101</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7026999999999994</v>
+        <v>-0.7026999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1.7131</v>
@@ -1468,13 +1468,13 @@
         <v>15.2254</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1749</v>
+        <v>-2.175</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4539</v>
+        <v>-1.4538</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7210000000000001</v>
+        <v>-0.7211000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.478499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0162</v>
+        <v>3.0258</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2848</v>
+        <v>3.9553</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2686</v>
+        <v>-0.9295</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5570000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.204</v>
+        <v>-0.1944</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8784</v>
+        <v>-0.2079</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3255</v>
+        <v>0.0135</v>
       </c>
       <c r="V14" t="n">
         <v>2.9072</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7855</v>
+        <v>2.0733</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4556</v>
+        <v>1.9026</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3299</v>
+        <v>0.1707</v>
       </c>
       <c r="G15" t="n">
         <v>2.4998</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3064</v>
+        <v>0.5942</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.262</v>
+        <v>0.1851</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5684</v>
+        <v>0.4092</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5857</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4379</v>
+        <v>1.039</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6842</v>
+        <v>0.6214</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2463</v>
+        <v>0.4175</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.1958</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2563</v>
+        <v>2.4456</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9395</v>
+        <v>-1.7515</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3382</v>
+        <v>1.3707</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9884</v>
+        <v>2.3819</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6502</v>
+        <v>-1.0112</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8576</v>
+        <v>-0.6767</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2679</v>
+        <v>0.0636</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5898</v>
+        <v>-0.7403</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6597</v>
+        <v>0.1502</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6548</v>
+        <v>-0.2692</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0049</v>
+        <v>0.4194</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3215</v>
+        <v>1.4997</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4552</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1337</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8064</v>
+        <v>0.3884</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2862</v>
+        <v>0.4549</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5203</v>
+        <v>-0.0665</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6941000000000001</v>
+        <v>-3.1958</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4456</v>
+        <v>-2.2563</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7515</v>
+        <v>-0.9395</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3707</v>
+        <v>-1.3382</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3819</v>
+        <v>-1.9884</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0112</v>
+        <v>0.6502</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6767</v>
+        <v>-1.8576</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0636</v>
+        <v>-0.2679</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7403</v>
+        <v>-1.5898</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0823</v>
+        <v>0.6102</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6044</v>
+        <v>0.4254</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5221</v>
+        <v>0.1847</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4997</v>
+        <v>2.3215</v>
       </c>
       <c r="W17" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-0.1337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.19</v>
+        <v>-0.3595</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7963</v>
+        <v>-0.7268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6063</v>
+        <v>0.3673</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.226</v>
+        <v>-0.1642</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0952</v>
+        <v>-0.6113</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1308</v>
+        <v>0.447</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5683</v>
+        <v>-0.7268</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6448</v>
+        <v>-0.7268</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6576</v>
+        <v>0.5626</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4504</v>
+        <v>0.1155</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2073</v>
+        <v>0.447</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5617</v>
+        <v>-0.1953</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8321</v>
+        <v>-0.1953</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8218</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2892</v>
+        <v>-0.5719</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6962</v>
+        <v>-0.1979</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.374</v>
       </c>
       <c r="G19" t="n">
         <v>0.7484</v>
@@ -1936,13 +1936,13 @@
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7709</v>
+        <v>0.4882</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5057</v>
+        <v>0.6117</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7348</v>
+        <v>-0.1235</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5034</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4212</v>
+        <v>-1.238</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7268</v>
+        <v>-1.7963</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3056</v>
+        <v>0.5583</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1642</v>
+        <v>-3.226</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6113</v>
+        <v>-2.0952</v>
       </c>
       <c r="I20" t="n">
-        <v>0.447</v>
+        <v>-1.1308</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7268</v>
+        <v>-1.5683</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7268</v>
+        <v>-1.6448</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5626</v>
+        <v>-1.6576</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1155</v>
+        <v>-0.4504</v>
       </c>
       <c r="O20" t="n">
-        <v>0.447</v>
+        <v>-1.2073</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2569</v>
+        <v>0.5137</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.2704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2569</v>
+        <v>0.7841</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8218</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1618</v>
+        <v>-2.3722</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.643</v>
+        <v>-1.6911</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4812</v>
+        <v>-0.681</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7165</v>
+        <v>-2.391</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2479</v>
+        <v>-1.618</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4686</v>
+        <v>-0.773</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6103</v>
+        <v>-1.9032</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6486</v>
+        <v>-1.2346</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0382</v>
+        <v>-0.6686</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1062</v>
+        <v>-0.4878</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5994</v>
+        <v>-0.3834</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5068</v>
+        <v>-0.1044</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.87</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0996</v>
+        <v>0.0835</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8172</v>
+        <v>0.0168</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2824</v>
+        <v>0.0667</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3252</v>
+        <v>-0.9347</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1647</v>
+        <v>-2.6088</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0264</v>
+        <v>-3.09</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1383</v>
+        <v>0.4812</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.391</v>
+        <v>-3.7165</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.618</v>
+        <v>-3.2479</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.773</v>
+        <v>-0.4686</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9032</v>
+        <v>-2.6103</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2346</v>
+        <v>-2.6486</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6686</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4878</v>
+        <v>-1.1062</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3834</v>
+        <v>-0.5994</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1044</v>
+        <v>-0.5068</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.709</v>
+        <v>0.6525</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3184</v>
+        <v>0.3701</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3906</v>
+        <v>0.2824</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9347</v>
+        <v>1.3252</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.990500000000001</v>
+        <v>-7.751</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3434</v>
+        <v>-4.5611</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6471</v>
+        <v>-3.1899</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3416</v>
@@ -2248,13 +2248,13 @@
         <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.971</v>
+        <v>0.2686</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.1406</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0481</v>
+        <v>0.4092</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3729</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.1714</v>
+        <v>-8.3749</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1289</v>
+        <v>-5.129</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0424</v>
+        <v>-3.2459</v>
       </c>
       <c r="G24" t="n">
         <v>-13.6498</v>
@@ -2326,13 +2326,13 @@
         <v>13.0505</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1751</v>
+        <v>2.9714</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7212000000000001</v>
+        <v>0.7210000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>1.454</v>
+        <v>2.2504</v>
       </c>
       <c r="V24" t="n">
         <v>4.4787</v>
